--- a/stories/arbres/TREE-TMP-002.xlsx
+++ b/stories/arbres/TREE-TMP-002.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nora marche sur le chemin de l'école, avec papa. Papa dit : il y a sept jours, dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora répète tout bas. Sept jours dans l'ordre. Les pieds font toc toc. Maman n'est pas loin. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+          <t>Nora marche sur le chemin de l'école, avec papa. Il y a sept jours, dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora répète tout bas. Sept jours dans l'ordre. Les pieds font toc toc. Maman n'est pas loin. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nora marche sur le chemin de l'école, avec papa.
+papa|Il y a sept jours, dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.
+narrateur|Nora répète tout bas. Sept jours dans l'ordre. Les pieds font toc toc. Maman n'est pas loin. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1489,6 +1513,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -1653,6 +1682,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Papa dit encore les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Tom écoute. Nora répète un jour : lundi. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1863,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le premier jour, c'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2036,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a entendu les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2227,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2394,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend les cubes. La couverture est douce. Avec les cubes, Nora en pose sept. Papa dit les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2585,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2752,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose une pomme près de l'assiette. La lumière est claire. On parle tout bas. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Lundi commence. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3086,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un yaourt près de l'assiette. Des miettes dorment sur la table. On range les jouets. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Papa serre Nora tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3253,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3420,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un morceau de pain près de l'assiette. Un chat miaule une fois. On s'assoit un moment. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3587,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3754,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend le livre. Le tissu est tout doux. Le livre a sept pages de couleurs. Sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3945,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3875,7 +3974,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Nora pose une pomme près de l'assiette. Les chaussures font toc toc. On respire, un, deux. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les doigts ont compté sept. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora range. Papa dit : c'est bien.</t>
+          <t>Nora pose une pomme près de l'assiette. Les chaussures font toc toc. On respire, un, deux. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les doigts ont compté sept. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4013,6 +4112,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose une pomme près de l'assiette. Les chaussures font toc toc. On respire, un, deux. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les doigts ont compté sept. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4280,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4447,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un yaourt près de l'assiette. La couverture est douce. On referme le sac. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Lundi commence. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On souffle. Nora sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4614,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4781,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un morceau de pain près de l'assiette. Une cloche tinte au loin. On essuie une miette. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4948,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5115,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend la dînette. Un ruisseau chante. À la dînette, sept petites assiettes. Papa nomme les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5306,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5473,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose une pomme près de l'assiette. Le bois sent le chaud. On met le doudou près. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5640,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5807,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un yaourt près de l'assiette. Une goutte tombe, ploc. On lace les chaussures. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les doigts ont compté sept. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Papa serre Nora tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5974,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6141,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un morceau de pain près de l'assiette. Le savon sent la fleur. On met le manteau. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Lundi commence. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6308,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6337,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Léa. Léa dit : mardi. Papa reprend les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora sourit. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+          <t>Nora rejoint Léa. Mardi. Papa reprend les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora sourit. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6475,13 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa.
+enfant-f|Mardi. Papa reprend les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.
+narrateur|Nora sourit. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6658,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Après vendredi, c'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6831,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Lundi à dimanche. Sept jours dans l'ordre. Nora a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6835,6 +7022,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6997,6 +7189,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend les cubes. Un chat miaule une fois. Nora empile. Lundi sur le cube. Sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7183,6 +7380,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7207,7 +7409,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Nora pose une pomme près de l'assiette. Le tissu est tout doux. On boit une gorgée. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora range. Papa dit : c'est bien.</t>
+          <t>Nora pose une pomme près de l'assiette. Le tissu est tout doux. On boit une gorgée. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7345,6 +7547,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose une pomme près de l'assiette. Le tissu est tout doux. On boit une gorgée. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7507,6 +7715,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7669,6 +7882,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un yaourt près de l'assiette. Une cuillère tinte. On feuillette le livre. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On souffle. Nora sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7831,6 +8049,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7993,6 +8216,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un morceau de pain près de l'assiette. Le sable est tiède. On referme le livre. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les doigts ont compté sept. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8155,6 +8383,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8317,6 +8550,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend le livre. Le savon mousse entre les doigts. Nora touche le papier. Mardi. Les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8503,6 +8741,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8665,6 +8908,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose une pomme près de l'assiette. Un rire court, tout petit. On pose le ballon. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Lundi commence. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8827,6 +9075,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8989,6 +9242,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un yaourt près de l'assiette. Le papier froisse, chut. On secoue le sable. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Papa serre Nora tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9151,6 +9409,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9313,6 +9576,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un morceau de pain près de l'assiette. L'herbe chatouille le mollet. On caresse le tissu. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9475,6 +9743,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9637,6 +9910,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend la dînette. Une goutte tombe, ploc. Une tasse. Nora dit jeudi. Papa reprend les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9823,6 +10101,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9847,7 +10130,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Nora pose une pomme près de l'assiette. Un pigeon roucoule. On tend la main. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les doigts ont compté sept. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora range. Papa dit : c'est bien.</t>
+          <t>Nora pose une pomme près de l'assiette. Un pigeon roucoule. On tend la main. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les doigts ont compté sept. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9985,6 +10268,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose une pomme près de l'assiette. Un pigeon roucoule. On tend la main. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les doigts ont compté sept. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10147,6 +10436,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10309,6 +10603,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un yaourt près de l'assiette. La fenêtre vibre un peu. On chante un petit air. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Lundi commence. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On souffle. Nora sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10471,6 +10770,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10633,6 +10937,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un morceau de pain près de l'assiette. Le lait est froid dans le verre. On compte jusqu'à trois. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10795,6 +11104,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10957,6 +11271,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Sami compte sur ses doigts. Sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora répète : mercredi. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11133,6 +11452,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Le dernier jour, c'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -11301,6 +11625,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Papa sourit. Sept jours dans l'ordre. Nora retient dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11487,6 +11816,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11649,6 +11983,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend les cubes. L'eau fait un petit bruit. Les cubes tombent. On recommence les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11835,6 +12174,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11997,6 +12341,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose une pomme près de l'assiette. La corde du sac est rêche. On montre du doigt. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12159,6 +12508,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12321,6 +12675,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un yaourt près de l'assiette. Le savon mousse entre les doigts. On range la chaise. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les doigts ont compté sept. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Papa serre Nora tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12483,6 +12842,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12645,6 +13009,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un morceau de pain près de l'assiette. Un ruisseau chante. On range un objet. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Lundi commence. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12807,6 +13176,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12969,6 +13343,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend le livre. La terre est un peu humide. Le livre se ferme. Nora dit vendredi. Sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13155,6 +13534,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13179,7 +13563,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Nora pose une pomme près de l'assiette. La laine gratte un peu. On se tient la main. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora range. Papa dit : c'est bien.</t>
+          <t>Nora pose une pomme près de l'assiette. La laine gratte un peu. On se tient la main. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13317,6 +13701,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose une pomme près de l'assiette. La laine gratte un peu. On se tient la main. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13479,6 +13869,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13641,6 +14036,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un yaourt près de l'assiette. Un pain croustille. On dit merci. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On souffle. Nora sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13803,6 +14203,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13965,6 +14370,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un morceau de pain près de l'assiette. Le savon glisse. On souffle doucement. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les doigts ont compté sept. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14127,6 +14537,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14289,6 +14704,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend la dînette. L'herbe chatouille le mollet. Nora range. Samedi, dimanche. Les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14475,6 +14895,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14637,6 +15062,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose une pomme près de l'assiette. Une plume vole. On écoute jusqu'au bout. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Lundi commence. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14799,6 +15229,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14961,6 +15396,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un yaourt près de l'assiette. Le banc est lisse. On attend son tour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Papa serre Nora tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15123,6 +15563,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15285,6 +15730,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un morceau de pain près de l'assiette. Un grelot sonne. On sourit ensemble. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15447,6 +15897,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15465,7 +15920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15482,6 +15937,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-TMP-002.xlsx
+++ b/stories/arbres/TREE-TMP-002.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Nora répète tout bas. Sept jours dans l'ordre. Les pieds font toc toc. Maman n'est pas loin. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1520,6 +1526,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1687,6 +1694,7 @@
           <t>narrateur|Nora rejoint Tom. Papa dit encore les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Tom écoute. Nora répète un jour : lundi. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1870,6 +1878,7 @@
           <t>narrateur|Le premier jour, c'est quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2041,6 +2050,7 @@
           <t>narrateur|Nora a entendu les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2232,6 +2242,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2399,6 +2410,7 @@
           <t>narrateur|Nora prend les cubes. La couverture est douce. Avec les cubes, Nora en pose sept. Papa dit les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2590,6 +2602,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2757,6 +2770,7 @@
           <t>narrateur|Nora pose une pomme près de l'assiette. La lumière est claire. On parle tout bas. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Lundi commence. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3106,7 @@
           <t>narrateur|Nora pose un yaourt près de l'assiette. Des miettes dorment sur la table. On range les jouets. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Papa serre Nora tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3274,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3442,7 @@
           <t>narrateur|Nora pose un morceau de pain près de l'assiette. Un chat miaule une fois. On s'assoit un moment. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3610,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3759,6 +3778,7 @@
           <t>narrateur|Nora prend le livre. Le tissu est tout doux. Le livre a sept pages de couleurs. Sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3950,6 +3970,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4118,6 +4139,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4285,6 +4307,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4452,6 +4475,7 @@
           <t>narrateur|Nora pose un yaourt près de l'assiette. La couverture est douce. On referme le sac. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Lundi commence. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On souffle. Nora sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4619,6 +4643,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4786,6 +4811,7 @@
           <t>narrateur|Nora pose un morceau de pain près de l'assiette. Une cloche tinte au loin. On essuie une miette. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4953,6 +4979,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5120,6 +5147,7 @@
           <t>narrateur|Nora prend la dînette. Un ruisseau chante. À la dînette, sept petites assiettes. Papa nomme les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5311,6 +5339,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5478,6 +5507,7 @@
           <t>narrateur|Nora pose une pomme près de l'assiette. Le bois sent le chaud. On met le doudou près. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5645,6 +5675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5812,6 +5843,7 @@
           <t>narrateur|Nora pose un yaourt près de l'assiette. Une goutte tombe, ploc. On lace les chaussures. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les doigts ont compté sept. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Papa serre Nora tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5979,6 +6011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6146,6 +6179,7 @@
           <t>narrateur|Nora pose un morceau de pain près de l'assiette. Le savon sent la fleur. On met le manteau. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Lundi commence. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6313,6 +6347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6482,6 +6517,7 @@
 narrateur|Nora sourit. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6665,6 +6701,7 @@
           <t>narrateur|Après vendredi, c'est quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6836,6 +6873,7 @@
           <t>narrateur|Lundi à dimanche. Sept jours dans l'ordre. Nora a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7027,6 +7065,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7194,6 +7233,7 @@
           <t>narrateur|Nora prend les cubes. Un chat miaule une fois. Nora empile. Lundi sur le cube. Sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7385,6 +7425,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7553,6 +7594,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7762,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +7930,7 @@
           <t>narrateur|Nora pose un yaourt près de l'assiette. Une cuillère tinte. On feuillette le livre. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On souffle. Nora sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8098,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8266,7 @@
           <t>narrateur|Nora pose un morceau de pain près de l'assiette. Le sable est tiède. On referme le livre. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les doigts ont compté sept. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8434,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8602,7 @@
           <t>narrateur|Nora prend le livre. Le savon mousse entre les doigts. Nora touche le papier. Mardi. Les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8794,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8913,6 +8962,7 @@
           <t>narrateur|Nora pose une pomme près de l'assiette. Un rire court, tout petit. On pose le ballon. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Lundi commence. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9298,7 @@
           <t>narrateur|Nora pose un yaourt près de l'assiette. Le papier froisse, chut. On secoue le sable. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Papa serre Nora tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9634,7 @@
           <t>narrateur|Nora pose un morceau de pain près de l'assiette. L'herbe chatouille le mollet. On caresse le tissu. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9802,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +9970,7 @@
           <t>narrateur|Nora prend la dînette. Une goutte tombe, ploc. Une tasse. Nora dit jeudi. Papa reprend les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10162,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10274,6 +10331,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10441,6 +10499,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10608,6 +10667,7 @@
           <t>narrateur|Nora pose un yaourt près de l'assiette. La fenêtre vibre un peu. On chante un petit air. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Lundi commence. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On souffle. Nora sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10775,6 +10835,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10942,6 +11003,7 @@
           <t>narrateur|Nora pose un morceau de pain près de l'assiette. Le lait est froid dans le verre. On compte jusqu'à trois. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11109,6 +11171,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11276,6 +11339,7 @@
           <t>narrateur|Nora rejoint Sami. Sami compte sur ses doigts. Sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora répète : mercredi. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11459,6 +11523,7 @@
           <t>narrateur|Le dernier jour, c'est quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11630,6 +11695,7 @@
           <t>narrateur|Papa sourit. Sept jours dans l'ordre. Nora retient dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11821,6 +11887,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11988,6 +12055,7 @@
           <t>narrateur|Nora prend les cubes. L'eau fait un petit bruit. Les cubes tombent. On recommence les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12179,6 +12247,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12346,6 +12415,7 @@
           <t>narrateur|Nora pose une pomme près de l'assiette. La corde du sac est rêche. On montre du doigt. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12513,6 +12583,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12680,6 +12751,7 @@
           <t>narrateur|Nora pose un yaourt près de l'assiette. Le savon mousse entre les doigts. On range la chaise. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les doigts ont compté sept. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Papa serre Nora tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12847,6 +12919,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13014,6 +13087,7 @@
           <t>narrateur|Nora pose un morceau de pain près de l'assiette. Un ruisseau chante. On range un objet. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Lundi commence. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13181,6 +13255,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13348,6 +13423,7 @@
           <t>narrateur|Nora prend le livre. La terre est un peu humide. Le livre se ferme. Nora dit vendredi. Sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13539,6 +13615,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13707,6 +13784,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13874,6 +13952,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14041,6 +14120,7 @@
           <t>narrateur|Nora pose un yaourt près de l'assiette. Un pain croustille. On dit merci. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On souffle. Nora sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14208,6 +14288,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14375,6 +14456,7 @@
           <t>narrateur|Nora pose un morceau de pain près de l'assiette. Le savon glisse. On souffle doucement. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les doigts ont compté sept. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14542,6 +14624,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14709,6 +14792,7 @@
           <t>narrateur|Nora prend la dînette. L'herbe chatouille le mollet. Nora range. Samedi, dimanche. Les sept jours dans l'ordre. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14900,6 +14984,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15067,6 +15152,7 @@
           <t>narrateur|Nora pose une pomme près de l'assiette. Une plume vole. On écoute jusqu'au bout. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Lundi commence. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Nora dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15234,6 +15320,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15401,6 +15488,7 @@
           <t>narrateur|Nora pose un yaourt près de l'assiette. Le banc est lisse. On attend son tour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Dimanche termine. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Papa serre Nora tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15568,6 +15656,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15735,6 +15824,7 @@
           <t>narrateur|Nora pose un morceau de pain près de l'assiette. Un grelot sonne. On sourit ensemble. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. On a répété un jour. Les sept jours dans l'ordre : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15902,6 +15992,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15920,7 +16011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15944,6 +16035,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15958,7 +16063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16145,6 +16250,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
